--- a/data/trans_orig/P13A_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P13A_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según días que sufre dolor de cabeza al mes en 2023</t>
+          <t>Población según cuántos días al mes sufre dolor de cabeza en 2023 (tasa de respuesta: 99,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15793</t>
+          <t>15518</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17743</t>
+          <t>18424</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36426</t>
+          <t>37157</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24847</t>
+          <t>25190</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45967</t>
+          <t>46164</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9308</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24134</t>
+          <t>24888</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25564</t>
+          <t>25669</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41601</t>
+          <t>41163</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37525</t>
+          <t>38234</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60411</t>
+          <t>59295</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77147</t>
+          <t>77354</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>115295</t>
+          <t>114321</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>141610</t>
+          <t>142071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>176787</t>
+          <t>176791</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>227606</t>
+          <t>224669</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>281272</t>
+          <t>280071</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>492303</t>
+          <t>492637</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>533600</t>
+          <t>534727</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>438185</t>
+          <t>435424</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>477153</t>
+          <t>475541</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>941709</t>
+          <t>943493</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1000697</t>
+          <t>1003509</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,8%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26581</t>
+          <t>26490</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34920</t>
+          <t>35788</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58364</t>
+          <t>60020</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>38971</t>
+          <t>38856</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>77440</t>
+          <t>78097</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>7027</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24878</t>
+          <t>24551</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36566</t>
+          <t>36109</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59196</t>
+          <t>59054</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40683</t>
+          <t>40358</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77351</t>
+          <t>77692</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82139</t>
+          <t>76688</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>203665</t>
+          <t>203788</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>206588</t>
+          <t>207195</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>249210</t>
+          <t>250973</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>253480</t>
+          <t>261697</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>445369</t>
+          <t>443200</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>947306</t>
+          <t>950462</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1089368</t>
+          <t>1101445</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>612710</t>
+          <t>612699</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>659945</t>
+          <t>662880</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1566317</t>
+          <t>1565262</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1823683</t>
+          <t>1811694</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,41%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3550</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15419</t>
+          <t>16724</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>15332</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45610</t>
+          <t>44485</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24692</t>
+          <t>24969</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53402</t>
+          <t>54248</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13389</t>
+          <t>13908</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36386</t>
+          <t>36261</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18991</t>
+          <t>20407</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59989</t>
+          <t>60263</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>40232</t>
+          <t>40771</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>85052</t>
+          <t>84347</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>123183</t>
+          <t>124126</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>170504</t>
+          <t>171310</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>260952</t>
+          <t>263983</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>659363</t>
+          <t>654733</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>395327</t>
+          <t>400409</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>996129</t>
+          <t>967166</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>59,18%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>501395</t>
+          <t>498291</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>551828</t>
+          <t>551146</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>236609</t>
+          <t>237627</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>579047</t>
+          <t>575845</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>574683</t>
+          <t>603995</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1120041</t>
+          <t>1118404</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,44%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>12040</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35435</t>
+          <t>35388</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68969</t>
+          <t>67446</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40760</t>
+          <t>40339</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73748</t>
+          <t>75513</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22490</t>
+          <t>21669</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49066</t>
+          <t>49304</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51753</t>
+          <t>51357</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>83458</t>
+          <t>83387</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>83128</t>
+          <t>81905</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>123186</t>
+          <t>120679</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>123207</t>
+          <t>122573</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>171501</t>
+          <t>172592</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>274327</t>
+          <t>272868</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>499164</t>
+          <t>493984</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>411453</t>
+          <t>409467</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>642887</t>
+          <t>652514</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,48%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>709955</t>
+          <t>710458</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>764262</t>
+          <t>766736</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>501797</t>
+          <t>509635</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>687809</t>
+          <t>688737</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1227707</t>
+          <t>1206188</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1437454</t>
+          <t>1441899</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,76%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25102</t>
+          <t>25203</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>51787</t>
+          <t>51393</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>123979</t>
+          <t>123257</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>181294</t>
+          <t>183039</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>158378</t>
+          <t>161946</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>219326</t>
+          <t>223357</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>62767</t>
+          <t>64389</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>109731</t>
+          <t>108457</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>154255</t>
+          <t>154477</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>216058</t>
+          <t>218063</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>232956</t>
+          <t>230145</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>313274</t>
+          <t>313323</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>405602</t>
+          <t>420364</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>602100</t>
+          <t>603837</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>939748</t>
+          <t>943842</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1584187</t>
+          <t>1715778</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1435920</t>
+          <t>1450980</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2281642</t>
+          <t>2217312</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2715355</t>
+          <t>2713849</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2953391</t>
+          <t>2934164</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1779155</t>
+          <t>1681044</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2343231</t>
+          <t>2339168</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4505642</t>
+          <t>4464031</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5221174</t>
+          <t>5191148</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P13A_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P13A_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>3948</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15518</t>
+          <t>15740</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25454</t>
+          <t>26776</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18424</t>
+          <t>19732</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37157</t>
+          <t>39485</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>33725</t>
+          <t>35422</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25190</t>
+          <t>25710</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46164</t>
+          <t>50610</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15399</t>
+          <t>15710</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9461</t>
+          <t>9613</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24888</t>
+          <t>25686</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>32829</t>
+          <t>36489</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25669</t>
+          <t>28516</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41163</t>
+          <t>45164</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,22 +908,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>48227</t>
+          <t>52199</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38234</t>
+          <t>41515</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59295</t>
+          <t>65213</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>93417</t>
+          <t>101547</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77354</t>
+          <t>83373</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>114321</t>
+          <t>125521</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>159274</t>
+          <t>169799</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>142071</t>
+          <t>153130</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>176791</t>
+          <t>191193</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>252691</t>
+          <t>271345</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>224669</t>
+          <t>244494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>280071</t>
+          <t>301925</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>515426</t>
+          <t>561545</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>492637</t>
+          <t>538577</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>534727</t>
+          <t>581747</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>456613</t>
+          <t>498454</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>435424</t>
+          <t>476593</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>475541</t>
+          <t>517080</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>972039</t>
+          <t>1060000</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>943493</t>
+          <t>1027040</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1003509</t>
+          <t>1093503</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>77,06%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>632513</t>
+          <t>687448</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>632513</t>
+          <t>687448</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>632513</t>
+          <t>687448</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>674170</t>
+          <t>731518</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>674170</t>
+          <t>731518</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>674170</t>
+          <t>731518</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1306683</t>
+          <t>1418966</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1306683</t>
+          <t>1418966</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1306683</t>
+          <t>1418966</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>14923</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26490</t>
+          <t>26815</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45187</t>
+          <t>50227</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35788</t>
+          <t>38835</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60020</t>
+          <t>65314</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>59955</t>
+          <t>65150</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>38856</t>
+          <t>52017</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>78097</t>
+          <t>84052</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14814</t>
+          <t>17679</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7027</t>
+          <t>11334</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24551</t>
+          <t>31181</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>46503</t>
+          <t>52850</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36109</t>
+          <t>40976</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59054</t>
+          <t>67185</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>61317</t>
+          <t>70529</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40358</t>
+          <t>56133</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77692</t>
+          <t>88173</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>152797</t>
+          <t>164430</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76688</t>
+          <t>138538</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>203788</t>
+          <t>196230</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>227591</t>
+          <t>249118</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>207195</t>
+          <t>225324</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>250973</t>
+          <t>273393</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>380388</t>
+          <t>413547</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>261697</t>
+          <t>378940</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>443200</t>
+          <t>451835</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,37%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1006955</t>
+          <t>847889</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>950462</t>
+          <t>809365</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1101445</t>
+          <t>874667</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>637751</t>
+          <t>717492</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>612699</t>
+          <t>687883</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>662880</t>
+          <t>744124</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1644707</t>
+          <t>1565382</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1565262</t>
+          <t>1523803</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1811694</t>
+          <t>1603773</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>75,84%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1189334</t>
+          <t>1044921</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1189334</t>
+          <t>1044921</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1189334</t>
+          <t>1044921</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>957032</t>
+          <t>1069686</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>957032</t>
+          <t>1069686</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>957032</t>
+          <t>1069686</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2146366</t>
+          <t>2114608</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2146366</t>
+          <t>2114608</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2146366</t>
+          <t>2114608</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16724</t>
+          <t>19159</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>31772</t>
+          <t>37488</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15332</t>
+          <t>27789</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44485</t>
+          <t>47740</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>40062</t>
+          <t>47880</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24969</t>
+          <t>37849</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54248</t>
+          <t>61056</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22411</t>
+          <t>24681</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13908</t>
+          <t>14875</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36261</t>
+          <t>37996</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41137</t>
+          <t>43529</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20407</t>
+          <t>32795</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>60263</t>
+          <t>57238</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>63548</t>
+          <t>68210</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>40771</t>
+          <t>53503</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>84347</t>
+          <t>86160</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>145793</t>
+          <t>168045</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>124126</t>
+          <t>145992</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>171310</t>
+          <t>198633</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>420586</t>
+          <t>246167</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>263983</t>
+          <t>222156</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>654733</t>
+          <t>272866</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>566380</t>
+          <t>414213</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>400409</t>
+          <t>381033</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>967166</t>
+          <t>451486</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>526420</t>
+          <t>598045</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>498291</t>
+          <t>566361</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>551146</t>
+          <t>622801</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>437734</t>
+          <t>480512</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>237627</t>
+          <t>453907</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>575845</t>
+          <t>506998</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>964155</t>
+          <t>1078556</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>603995</t>
+          <t>1037888</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1118404</t>
+          <t>1114546</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>69,28%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>702914</t>
+          <t>801163</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>702914</t>
+          <t>801163</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>702914</t>
+          <t>801163</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>931230</t>
+          <t>807696</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>931230</t>
+          <t>807696</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>931230</t>
+          <t>807696</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1634144</t>
+          <t>1608859</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1634144</t>
+          <t>1608859</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1634144</t>
+          <t>1608859</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12040</t>
+          <t>12589</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>49421</t>
+          <t>49875</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35388</t>
+          <t>37979</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67446</t>
+          <t>65202</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>55485</t>
+          <t>55823</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40339</t>
+          <t>42672</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75513</t>
+          <t>71256</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -2545,67 +2545,67 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>32156</t>
+          <t>33796</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21669</t>
+          <t>22550</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49304</t>
+          <t>50745</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>71565</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>59174</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>86623</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>6,46%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
           <t>5,34%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>68174</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>51357</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>83387</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>100330</t>
+          <t>105361</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>81905</t>
+          <t>87696</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>120679</t>
+          <t>126091</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>145574</t>
+          <t>152386</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>122573</t>
+          <t>128664</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>172592</t>
+          <t>178844</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>332743</t>
+          <t>283033</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>272868</t>
+          <t>255603</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>493984</t>
+          <t>308581</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>478317</t>
+          <t>435420</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>409467</t>
+          <t>402183</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>652514</t>
+          <t>477011</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>739513</t>
+          <t>793353</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>710458</t>
+          <t>764089</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>766736</t>
+          <t>819642</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>635578</t>
+          <t>703745</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>509635</t>
+          <t>676097</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>688737</t>
+          <t>732657</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1375090</t>
+          <t>1497097</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1206188</t>
+          <t>1456936</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1441899</t>
+          <t>1533195</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>73,23%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>923307</t>
+          <t>985483</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>923307</t>
+          <t>985483</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>923307</t>
+          <t>985483</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1085915</t>
+          <t>1108218</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1085915</t>
+          <t>1108218</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1085915</t>
+          <t>1108218</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2009222</t>
+          <t>2093701</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2009222</t>
+          <t>2093701</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2009222</t>
+          <t>2093701</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25203</t>
+          <t>29269</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>51393</t>
+          <t>55553</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>151834</t>
+          <t>164366</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>123257</t>
+          <t>142917</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>183039</t>
+          <t>188685</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>189227</t>
+          <t>204275</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>161946</t>
+          <t>177943</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>223357</t>
+          <t>233433</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>84779</t>
+          <t>91867</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64389</t>
+          <t>73525</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>108457</t>
+          <t>116379</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>188642</t>
+          <t>204432</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>154477</t>
+          <t>182657</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>218063</t>
+          <t>230380</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>273422</t>
+          <t>296299</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>230145</t>
+          <t>264888</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>313323</t>
+          <t>330452</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>537582</t>
+          <t>586408</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>420364</t>
+          <t>539350</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>603837</t>
+          <t>637824</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1140195</t>
+          <t>948117</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>943842</t>
+          <t>905681</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1715778</t>
+          <t>995157</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1677777</t>
+          <t>1534525</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1450980</t>
+          <t>1464905</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2217312</t>
+          <t>1598495</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2788314</t>
+          <t>2800833</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2713849</t>
+          <t>2744798</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2934164</t>
+          <t>2847721</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2167677</t>
+          <t>2400202</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1681044</t>
+          <t>2350329</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2339168</t>
+          <t>2449004</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>4955991</t>
+          <t>5201035</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4464031</t>
+          <t>5132037</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5191148</t>
+          <t>5276229</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>72,92%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3448068</t>
+          <t>3519016</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3448068</t>
+          <t>3519016</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3448068</t>
+          <t>3519016</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3648348</t>
+          <t>3717118</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3648348</t>
+          <t>3717118</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3648348</t>
+          <t>3717118</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7096416</t>
+          <t>7236134</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7096416</t>
+          <t>7236134</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7096416</t>
+          <t>7236134</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
